--- a/appium_testing/test_reports/travix_e2e_appium_report.xlsx
+++ b/appium_testing/test_reports/travix_e2e_appium_report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="72">
   <si>
     <t>TRAVIX APPIUM E2E AUTOMATION TEST REPORT</t>
   </si>
@@ -20,7 +20,7 @@
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>8/18/2026, 5:44:30 AM</t>
+    <t>8/18/2026, 5:55:28 AM</t>
   </si>
   <si>
     <t>Target Platform:</t>
@@ -98,7 +98,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-18T05:44:30.826Z</t>
+    <t>2026-08-18T05:55:28.790Z</t>
   </si>
   <si>
     <t>TC-USER-02</t>
@@ -111,9 +111,6 @@
   </si>
   <si>
     <t>Fare estimated at $18.50, female priority flag attached</t>
-  </si>
-  <si>
-    <t>2026-08-18T05:44:30.827Z</t>
   </si>
   <si>
     <t>TC-USER-03</t>
@@ -851,24 +848,24 @@
         <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
         <v>35</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>36</v>
-      </c>
-      <c r="E4" t="s">
-        <v>37</v>
       </c>
       <c r="F4">
         <v>620</v>
@@ -877,24 +874,24 @@
         <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
         <v>39</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>40</v>
-      </c>
-      <c r="E5" t="s">
-        <v>41</v>
       </c>
       <c r="F5">
         <v>1100</v>
@@ -903,24 +900,24 @@
         <v>27</v>
       </c>
       <c r="H5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s">
         <v>42</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>43</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>44</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>45</v>
-      </c>
-      <c r="E6" t="s">
-        <v>46</v>
       </c>
       <c r="F6">
         <v>480</v>
@@ -929,24 +926,24 @@
         <v>27</v>
       </c>
       <c r="H6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
         <v>47</v>
       </c>
-      <c r="B7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>48</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>49</v>
-      </c>
-      <c r="E7" t="s">
-        <v>50</v>
       </c>
       <c r="F7">
         <v>1350</v>
@@ -955,24 +952,24 @@
         <v>27</v>
       </c>
       <c r="H7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
         <v>51</v>
       </c>
-      <c r="B8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>52</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>53</v>
-      </c>
-      <c r="E8" t="s">
-        <v>54</v>
       </c>
       <c r="F8">
         <v>540</v>
@@ -981,24 +978,24 @@
         <v>27</v>
       </c>
       <c r="H8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
         <v>55</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>56</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>57</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>58</v>
-      </c>
-      <c r="E9" t="s">
-        <v>59</v>
       </c>
       <c r="F9">
         <v>790</v>
@@ -1007,24 +1004,24 @@
         <v>27</v>
       </c>
       <c r="H9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
         <v>60</v>
       </c>
-      <c r="B10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>61</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>62</v>
-      </c>
-      <c r="E10" t="s">
-        <v>63</v>
       </c>
       <c r="F10">
         <v>980</v>
@@ -1033,24 +1030,24 @@
         <v>27</v>
       </c>
       <c r="H10" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" t="s">
         <v>64</v>
       </c>
-      <c r="B11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>65</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>66</v>
-      </c>
-      <c r="E11" t="s">
-        <v>67</v>
       </c>
       <c r="F11">
         <v>1150</v>
@@ -1059,24 +1056,24 @@
         <v>27</v>
       </c>
       <c r="H11" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" t="s">
         <v>68</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>69</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>70</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>71</v>
-      </c>
-      <c r="E12" t="s">
-        <v>72</v>
       </c>
       <c r="F12">
         <v>2400</v>
@@ -1085,7 +1082,7 @@
         <v>27</v>
       </c>
       <c r="H12" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/appium_testing/test_reports/travix_e2e_appium_report.xlsx
+++ b/appium_testing/test_reports/travix_e2e_appium_report.xlsx
@@ -20,7 +20,7 @@
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>8/18/2026, 5:55:28 AM</t>
+    <t>8/18/2026, 6:20:31 AM</t>
   </si>
   <si>
     <t>Target Platform:</t>
@@ -98,7 +98,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-18T05:55:28.790Z</t>
+    <t>2026-08-18T06:20:31.102Z</t>
   </si>
   <si>
     <t>TC-USER-02</t>
